--- a/report/Phase1核心功能列表.xlsx
+++ b/report/Phase1核心功能列表.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Phase1 核心功能（三层级）" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="英文版-Roadmap1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,6 +126,22 @@
       <name val="Microsoft YaHei"/>
       <color rgb="0064748B"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="8.800000000000001"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00475569"/>
+      <sz val="8.4"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="10">
@@ -201,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -254,6 +271,21 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1576,4 +1608,481 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Phase 1 · Basic File Management（CHINA RIMS 英文版功能点 → 三层级总结）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>来源：CHINA RIMS SOLUTION PROPOSAL · Function Roadmap 1 —— 安全合规的手动文件上传与管理系统，确保 PI（个人信息）不出境 · OBJECTIVE：退役系统文件的手动上传/管理通道，PI 数据境内留存</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>业务场景</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>业务功能（英文原文）</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>业务功能（中文）</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>技术功能（实现层）</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>数据/存储层处理</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>合规控制点</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>文件管理</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>File import / export</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>文件导入 / 导出</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>上传：Web 端手动上传（批量/压缩包）→ 服务端校验（类型/大小/病毒可选）→ Azure Blob（境内区域账户）存储；导出：受控下载（SAS 限时链接），不经服务端中转</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Blob 附件账户（FNS 平面命名空间）；上传时登记元数据（原始文件名/大小/上传人/时间）；SHA-256 完整性指纹</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>PI 不出境：存储区域锁定中国区；下载走受控链路并留痕</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>Phase1 为手动上传，不做自动抽取（后续 Roadmap 演进）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>文件管理</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>File deletion</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>文件删除</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>逻辑删除（回收站机制，可恢复期内）+ 管理员物理清除（合规销毁）；删除需权限校验并记录操作人</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>逻辑删除标记 → 到期物理清除（Blob 删除 + 索引更新）；销毁留痕入审计日志</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>合规删除：删除动作可举证（谁/何时/删了什么）；配合保留期策略</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>文件管理</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>File metadata mgmt.</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>文件元数据管理</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>元数据模型：来源系统/文件分类/业务时间/关联业务单号/标签；元数据编辑与查询界面</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>元数据库（Azure SQL）存储；文件 ↔ 元数据 ↔ 来源系统三方关联索引</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>元数据含 PI 标记字段（为后续脱敏/加密演进预留）</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr"/>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>系统配置</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>User mgmt.</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>用户管理</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>用户账号全生命周期：创建/启用/禁用/重置；对接企业统一身份（SSO 登录自动关联本地账号）</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>用户表 + Entra ID OIDC 对接；首次登录自动建档（身份自动识别与关联）</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>账号操作（禁用/重置）全部留痕</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>系统配置</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>Role permission mgmt.</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>角色权限管理</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>RBAC 角色模型（管理员/上传员/查询员/审计员）；按角色控制菜单/按钮/数据三层权限</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>权限矩阵落元数据库；后端鉴权中间件（JWT Claims）+ 前端菜单/按钮渲染控制</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>最小权限原则；权限变更留痕</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>系统配置</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>Basic Data Mgmt.</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>基础数据管理</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>基础字典维护：来源系统清单、文件分类、保留期规则、标签字典等配置项管理界面</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>字典表 CRUD + 缓存；配置变更即生效（无需发版）</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>保留期规则为后续到期处置的输入</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr"/>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>系统日志</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>Operation Log</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>操作日志</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>记录全部用户操作：登录/上传/下载/删除/配置变更（谁/何时/操作/对象/结果/IP）</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>后端拦截埋点 → 日志表（追加式存储）</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>操作可追溯、不可抵赖</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr"/>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>系统日志</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>Audit Log</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>审计日志</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>面向合规审计的独立日志视图：按用户/时间/操作类型/文件检索；审计报表导出</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>审计日志独立存储（与操作日志分表）；导出受审计员权限控制</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>满足内外部审计调取（等保/内审）；导出本身也留痕</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr"/>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>价值与目标</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>PI does not leave the country</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>个人信息不出境（合规缺口闭环）</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>境内区域部署（全部组件中国区）；数据存储与访问链路境内闭环</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>存储区域锁定 + 出口管控</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>核心 OBJECTIVE——所有功能设计的首要约束</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr"/>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>价值与目标</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>Immediately usable channel for decommissioning projects</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>退役项目即刻可用的落地通道</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>Phase1 以手动上传起步：不依赖源系统改造，退役项目当周即可开始归档</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>先解决"有没有"，再演进"自动化"</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>对应 VALUE 第 2 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>价值与目标</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>Foundation for later automation</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>后续自动化的地基</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>Phase1 建立的元数据模型/权限体系/审计框架/存储结构，直接支撑后续 Roadmap 的自动迁移与湖仓检索</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>存储与元数据结构按湖仓架构预留（Blob→ADLS/Iceberg 演进路径）</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>对应 VALUE 第 3 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>读法：业务场景（3+1 类）→ 业务功能（英文原文对照）→ 技术功能（怎么实现，含数据/存储层与合规控制点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>与中文版功能列表的映射：File import ≈ F01-02 非结构化导入（手动版）；Metadata ≈ F02；User/Role ≈ F08；Operation/Audit Log ≈ F06；Deletion 为 Phase1 新增点（对应 F03 的简化版，本期做手动/逻辑删除，自动到期处置留待后续）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>英文版与中文版范围差异：英文 Roadmap 1 更聚焦"手动文件管理"（无批量抽取/在线检索/到期自动删除）——本表技术功能按 Azure B2 架构落地，后续 Roadmap 可平滑演进到自动迁移与湖仓检索</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A19:G19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/report/Phase1核心功能列表.xlsx
+++ b/report/Phase1核心功能列表.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -142,6 +142,17 @@
       <name val="Microsoft YaHei"/>
       <color rgb="0064748B"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="10">
@@ -218,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -286,6 +297,24 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -652,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -843,17 +872,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>确保迁移过程数据完整可追溯</t>
+          <t>多源异构数据接入与标准化</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>迁移前完整性基准记录</t>
+          <t>统一元数据模型</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>F01-04</t>
+          <t>F02-01</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -863,12 +892,12 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>模块 1</t>
+          <t>模块 2</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>源端行数/校验和/文件清单快照入台账（迁移举证基线）</t>
+          <t>统一元数据字段体系（字段定义/类型/来源系统编码）；元数据库 35 表落地</t>
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr"/>
@@ -881,108 +910,108 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>确保迁移过程数据完整可追溯</t>
+          <t>多源异构数据接入与标准化</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>迁移后完整性比对</t>
+          <t>来源系统信息绑定</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>F01-05</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
+          <t>F02-02</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>模块 2</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>记录接入时绑定源系统编码与退役系统档案；数据血缘（哪条记录来自哪个源）</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr"/>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>检索</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>QA/IT 人员日常基础数据查阅</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>关键词检索</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>F05-01</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>模块 1</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>目标端 vs 基线双向比对（行数/校验和）；差异报告；RAW→CURATED→LAKE→SERVE 四层转换中的清洗与分区归约</t>
-        </is>
-      </c>
-      <c r="H9" s="11" t="inlineStr"/>
-    </row>
-    <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>归档</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>多源异构数据接入与标准化</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>统一元数据模型</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>F02-01</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>模块 2</t>
+          <t>模块 5</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>统一元数据字段体系（字段定义/类型/来源系统编码）；元数据库 35 表落地</t>
+          <t>元数据驱动动态查询表单 → 查询代理（SQL 白名单+参数化拼装）→ Databricks SQL Warehouse（SERVE 层热表，分区裁剪）</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr"/>
     </row>
     <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>归档</t>
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>检索</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>多源异构数据接入与标准化</t>
+          <t>QA/IT 人员日常基础数据查阅</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>来源系统信息绑定</t>
+          <t>按系统名称检索</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>F02-02</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>F05-02</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>模块 2</t>
+          <t>模块 5</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>记录接入时绑定源系统编码与退役系统档案；数据血缘（哪条记录来自哪个源）</t>
+          <t>系统下拉（来源系统绑定 F02-02）+ catalog-per-system 路由到对应归档库</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr"/>
@@ -1000,12 +1029,12 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>关键词检索</t>
+          <t>按业务时间检索</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>F05-01</t>
+          <t>F05-03</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -1020,7 +1049,7 @@
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>元数据驱动动态查询表单 → 查询代理（SQL 白名单+参数化拼装）→ Databricks SQL Warehouse（SERVE 层热表，分区裁剪）</t>
+          <t>时间区间 → Iceberg 分区裁剪（业务时间分区列）；避免全表扫描</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr"/>
@@ -1038,12 +1067,12 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>按系统名称检索</t>
+          <t>检索结果列表展示</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>F05-02</t>
+          <t>F05-04</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -1058,7 +1087,7 @@
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>系统下拉（来源系统绑定 F02-02）+ catalog-per-system 路由到对应归档库</t>
+          <t>React 动态表格（元数据驱动列渲染/分页/排序/大批量懒加载）</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr"/>
@@ -1076,88 +1105,88 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>按业务时间检索</t>
+          <t>原始文件在线预览</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>F05-03</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
+          <t>F05-05</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>模块 5</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>后端签发 SAS → 前端直连 Blob 预览（图片/常见文档），不经服务端中转</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr"/>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>管控</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>企业用户统一身份认证与访问</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>企业 SSO 集成</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>F08-03</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>模块 5</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>时间区间 → Iceberg 分区裁剪（业务时间分区列）；避免全表扫描</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="inlineStr"/>
-    </row>
-    <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>检索</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>QA/IT 人员日常基础数据查阅</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>检索结果列表展示</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>F05-04</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>模块 5</t>
+          <t>模块 8</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>React 动态表格（元数据驱动列渲染/分页/排序/大批量懒加载）</t>
+          <t>Entra ID OIDC 对接；JWT 角色 Claims；登录态管理</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr"/>
     </row>
     <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>检索</t>
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>管控</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>QA/IT 人员日常基础数据查阅</t>
+          <t>企业用户统一身份认证与访问</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>原始文件在线预览</t>
+          <t>用户身份自动识别与关联</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>F05-05</t>
+          <t>F08-04</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -1167,12 +1196,12 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>模块 5</t>
+          <t>模块 8</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>后端签发 SAS → 前端直连 Blob 预览（图片/常见文档），不经服务端中转</t>
+          <t>企业身份 → RIMS 用户自动关联（首次登录建档）</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr"/>
@@ -1190,17 +1219,17 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>企业 SSO 集成</t>
+          <t>登录状态与异常访问控制</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>F08-03</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>F08-05</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
@@ -1210,7 +1239,7 @@
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>Entra ID OIDC 对接；JWT 角色 Claims；登录态管理</t>
+          <t>会话超时/认证失败锁定/异常登录记录</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr"/>
@@ -1223,22 +1252,22 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>企业用户统一身份认证与访问</t>
+          <t>基础运维核查与权限管理</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>用户身份自动识别与关联</t>
+          <t>基础角色权限配置</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>F08-04</t>
-        </is>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>F08-01</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
@@ -1248,7 +1277,7 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>企业身份 → RIMS 用户自动关联（首次登录建档）</t>
+          <t>RBAC 基础三角色（管理员/查询员/审计员）；页面+数据双层权限</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr"/>
@@ -1261,17 +1290,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>企业用户统一身份认证与访问</t>
+          <t>基础运维核查与权限管理</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>登录状态与异常访问控制</t>
+          <t>用户账号管理</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>F08-05</t>
+          <t>F08-02</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
@@ -1286,7 +1315,7 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>会话超时/认证失败锁定/异常登录记录</t>
+          <t>账号启用/禁用/重置（SSO 体系下的本地映射管理）</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr"/>
@@ -1299,17 +1328,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>基础运维核查与权限管理</t>
+          <t>基础运维核查与审计调取</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>基础角色权限配置</t>
+          <t>归档/查询/导出操作日志记录</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>F08-01</t>
+          <t>F06-01/02/03</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -1319,96 +1348,104 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>模块 8</t>
+          <t>模块 6</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>RBAC 基础三角色（管理员/查询员/审计员）；页面+数据双层权限</t>
+          <t>后端拦截埋点（谁/何时/操作了什么/结果）→ 审计表；查询界面按时间/用户/类型筛选</t>
         </is>
       </c>
       <c r="H20" s="11" t="inlineStr"/>
     </row>
     <row r="21" ht="44" customHeight="1">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>管控</t>
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>暂缓（Phase1.1/Phase2）</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>基础运维核查与权限管理</t>
+          <t>满足数据不出境合规要求</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>用户账号管理</t>
+          <t>数据加密存储 + 密钥管理</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>F08-02</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>F04-01/02</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>模块 8</t>
+          <t>模块 4</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>账号启用/禁用/重置（SSO 体系下的本地映射管理）</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="inlineStr"/>
+          <t>（后续）Key Vault CMK + 字段级 aes_encrypt + 掩码函数</t>
+        </is>
+      </c>
+      <c r="H21" s="17" t="inlineStr">
+        <is>
+          <t>依赖：PII 字段分级清单与合规口径定稿（法务）——先以 Azure 平台级 SSE 过渡，不阻塞上线</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="44" customHeight="1">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>管控</t>
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>暂缓（Phase1.1/Phase2）</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>基础运维核查与审计调取</t>
+          <t>确保归档数据可恢复</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>归档/查询/导出操作日志记录</t>
+          <t>数据备份管理 + 异地灾备</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>F06-01/02/03</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>F04-03/04</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>模块 6</t>
+          <t>模块 4</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>后端拦截埋点（谁/何时/操作了什么/结果）→ 审计表；查询界面按时间/用户/类型筛选</t>
-        </is>
-      </c>
-      <c r="H22" s="11" t="inlineStr"/>
+          <t>（后续）SQL PITR + 存储冗余 + 灾备演练</t>
+        </is>
+      </c>
+      <c r="H22" s="17" t="inlineStr">
+        <is>
+          <t>依赖：基础设施与灾备方案评审（平台团队）——Phase1 用云平台默认冗余过渡</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="44" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>管控</t>
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>暂缓（Phase1.1/Phase2）</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -1418,185 +1455,149 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
+          <t>Legal Hold 冻结</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>F03-02</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>模块 3</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>（后续）Hold/Release + 豁免 + 留痕（在处置引擎上扩展）</t>
+        </is>
+      </c>
+      <c r="H23" s="17" t="inlineStr">
+        <is>
+          <t>依赖：Legal Hold 触发条件与审批流程定义（法务）——处置引擎（F03-01）本期交付，Hold 作为其扩展下期补</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>暂缓（Phase1.1/Phase2）</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>确保迁移过程数据完整可追溯</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>迁移前基准记录 + 迁移后完整性比对</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="inlineStr">
+        <is>
+          <t>F01-04/05</t>
+        </is>
+      </c>
+      <c r="E24" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F24" s="29" t="inlineStr">
+        <is>
+          <t>模块 1</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>（后续）基准快照 + 双向比对 + 差异报告</t>
+        </is>
+      </c>
+      <c r="H24" s="17" t="inlineStr">
+        <is>
+          <t>依赖：数据质量基线与对账方案确定——Phase1 先以导入成功行数核对过渡，不阻塞上线</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>暂缓（Phase1.1/Phase2）</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>归档记录定期删除与合规保留</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
           <t>保留期限到期自动删除</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D25" s="27" t="inlineStr">
         <is>
           <t>F03-01</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="E25" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F25" s="29" t="inlineStr">
         <is>
           <t>模块 3</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>保留策略配置 → 到期扫描 → DROP PARTITION（秒级元数据删除）→ VACUUM（物理清除）→ 审计留痕</t>
-        </is>
-      </c>
-      <c r="H23" s="11" t="inlineStr"/>
-    </row>
-    <row r="24" ht="44" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>暂缓（Phase1.1/Phase2）</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>满足数据不出境合规要求</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>数据加密存储 + 密钥管理</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>F04-01/02</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>模块 4</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>（后续）Key Vault CMK + 字段级 aes_encrypt + 掩码函数</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>依赖：PII 字段分级清单与合规口径定稿（法务）——先以 Azure 平台级 SSE 过渡，不阻塞上线</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="44" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>暂缓（Phase1.1/Phase2）</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>确保归档数据可恢复</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>数据备份管理 + 异地灾备</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>F04-03/04</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>模块 4</t>
-        </is>
-      </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>（后续）SQL PITR + 存储冗余 + 灾备演练</t>
+          <t>（后续）保留策略→到期扫描→DROP PARTITION→VACUUM→留痕</t>
         </is>
       </c>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>依赖：基础设施与灾备方案评审（平台团队）——Phase1 用云平台默认冗余过渡</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="44" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>暂缓（Phase1.1/Phase2）</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>归档记录定期删除与合规保留</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Legal Hold 冻结</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>F03-02</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>模块 3</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>（后续）Hold/Release + 豁免 + 留痕（在处置引擎上扩展）</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>依赖：Legal Hold 触发条件与审批流程定义（法务）——处置引擎（F03-01）本期交付，Hold 作为其扩展下期补</t>
+          <t>依赖：保留期规则与处置审批流程定稿——Phase1 以文件手动删除（回收站）过渡</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="44" customHeight="1"/>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>纳入统计：16 项技术功能（P0×10：F01-01/03、F05-01/02/03/04、F08-01/03、F06 三合一；P1×6：F01-02、F02-01/02、F05-05、F08-02/04/05）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>纳入统计：19 项技术功能（P0×11：F01-01/03/05、F05-01/02/03/04、F08-01/03、F06 三合一；P1×8：F01-02/04、F02-01/02、F05-05、F08-02/04/05、F03-01）</t>
+          <t>暂缓统计：5 组 10 项（加密×2 / 备份灾备×2 / Legal Hold×1 / 迁移完整性校验×2 / 到期自动删除×1）——均有过渡方案，不阻塞 Phase1 上线</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>暂缓统计：3 组 7 项（加密×2 / 备份灾备×2 / Legal Hold×1 + 其中 F06 已合并计入）——均有平台级过渡方案，不阻塞 Phase1 上线</t>
+          <t>三层级读法：业务场景（为什么做）→ 业务功能（做什么）→ 技术功能（怎么做，含数据层处理：四层转换/分区/SAS）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>三层级读法：业务场景（为什么做）→ 业务功能（做什么）→ 技术功能（怎么做，含数据层处理：四层转换/分区/对账/SAS/处置引擎）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>与计划对应：本表 P0+P1 = 项目执行计划2.xlsx 周计划的开发范围；暂缓项在 Phase1.1（W13+）或 Phase2 排期</t>
-        </is>
-      </c>
-    </row>
+          <t>与计划对应：本表 P0+P1 = 项目执行计划2 周计划的开发范围；暂缓项在 Phase1.1（W13+）或 Phase2 排期</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A30:H30"/>

--- a/report/Phase1核心功能列表.xlsx
+++ b/report/Phase1核心功能列表.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -154,8 +154,50 @@
       <color rgb="001E3A8A"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="005B21B6"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -202,8 +244,33 @@
         <fgColor rgb="00E2E8F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDE9FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAFAFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -225,11 +292,92 @@
         <color rgb="00CBD5E1"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="medium">
+        <color rgb="0094A3B8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0094A3B8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="0094A3B8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0094A3B8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="0094A3B8"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -316,6 +464,133 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -681,7 +956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -695,7 +970,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>Phase 1 开发 · 核心功能列表（业务场景 → 业务功能 → 技术功能）</t>
         </is>
@@ -708,55 +983,55 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>业务场景</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>业务功能</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>技术功能（实现层）</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr">
         <is>
           <t>对应功能列表编号</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="31" t="inlineStr">
         <is>
           <t>所属模块</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t>技术要点/数据层处理</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="31" t="inlineStr">
         <is>
           <t>暂缓原因（如暂缓）</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>归档</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>退役系统历史数据全量入库归档</t>
         </is>
@@ -788,17 +1063,9 @@
       </c>
       <c r="H5" s="11" t="inlineStr"/>
     </row>
-    <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>归档</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>退役系统历史数据全量入库归档</t>
-        </is>
-      </c>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="33" t="n"/>
+      <c r="B6" s="33" t="n"/>
       <c r="C6" s="6" t="inlineStr">
         <is>
           <t>非结构化文件及离线包批量导入</t>
@@ -826,17 +1093,9 @@
       </c>
       <c r="H6" s="11" t="inlineStr"/>
     </row>
-    <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>归档</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>退役系统历史数据全量入库归档</t>
-        </is>
-      </c>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="33" t="n"/>
+      <c r="B7" s="69" t="n"/>
       <c r="C7" s="6" t="inlineStr">
         <is>
           <t>数据导入规则配置</t>
@@ -864,13 +1123,9 @@
       </c>
       <c r="H7" s="11" t="inlineStr"/>
     </row>
-    <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>归档</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="33" t="n"/>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>多源异构数据接入与标准化</t>
         </is>
@@ -902,51 +1157,43 @@
       </c>
       <c r="H8" s="11" t="inlineStr"/>
     </row>
-    <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>归档</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>多源异构数据接入与标准化</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="69" t="n"/>
+      <c r="B9" s="69" t="n"/>
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>来源系统信息绑定</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="38" t="inlineStr">
         <is>
           <t>F02-02</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="39" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="40" t="inlineStr">
         <is>
           <t>模块 2</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="41" t="inlineStr">
         <is>
           <t>记录接入时绑定源系统编码与退役系统档案；数据血缘（哪条记录来自哪个源）</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr"/>
-    </row>
-    <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="H9" s="42" t="inlineStr"/>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="43" t="inlineStr">
         <is>
           <t>检索</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>QA/IT 人员日常基础数据查阅</t>
         </is>
@@ -978,17 +1225,9 @@
       </c>
       <c r="H10" s="11" t="inlineStr"/>
     </row>
-    <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>检索</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>QA/IT 人员日常基础数据查阅</t>
-        </is>
-      </c>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="33" t="n"/>
+      <c r="B11" s="33" t="n"/>
       <c r="C11" s="6" t="inlineStr">
         <is>
           <t>按系统名称检索</t>
@@ -1016,17 +1255,9 @@
       </c>
       <c r="H11" s="11" t="inlineStr"/>
     </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>检索</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>QA/IT 人员日常基础数据查阅</t>
-        </is>
-      </c>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="33" t="n"/>
+      <c r="B12" s="33" t="n"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
           <t>按业务时间检索</t>
@@ -1054,17 +1285,9 @@
       </c>
       <c r="H12" s="11" t="inlineStr"/>
     </row>
-    <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>检索</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>QA/IT 人员日常基础数据查阅</t>
-        </is>
-      </c>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="33" t="n"/>
+      <c r="B13" s="33" t="n"/>
       <c r="C13" s="6" t="inlineStr">
         <is>
           <t>检索结果列表展示</t>
@@ -1092,51 +1315,43 @@
       </c>
       <c r="H13" s="11" t="inlineStr"/>
     </row>
-    <row r="14" ht="44" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>检索</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>QA/IT 人员日常基础数据查阅</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="69" t="n"/>
+      <c r="B14" s="69" t="n"/>
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>原始文件在线预览</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="38" t="inlineStr">
         <is>
           <t>F05-05</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="39" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="40" t="inlineStr">
         <is>
           <t>模块 5</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="41" t="inlineStr">
         <is>
           <t>后端签发 SAS → 前端直连 Blob 预览（图片/常见文档），不经服务端中转</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr"/>
-    </row>
-    <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="H14" s="42" t="inlineStr"/>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="44" t="inlineStr">
         <is>
           <t>管控</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>企业用户统一身份认证与访问</t>
         </is>
@@ -1168,17 +1383,9 @@
       </c>
       <c r="H15" s="11" t="inlineStr"/>
     </row>
-    <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>管控</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>企业用户统一身份认证与访问</t>
-        </is>
-      </c>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="33" t="n"/>
+      <c r="B16" s="33" t="n"/>
       <c r="C16" s="6" t="inlineStr">
         <is>
           <t>用户身份自动识别与关联</t>
@@ -1206,17 +1413,9 @@
       </c>
       <c r="H16" s="11" t="inlineStr"/>
     </row>
-    <row r="17" ht="44" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>管控</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>企业用户统一身份认证与访问</t>
-        </is>
-      </c>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="33" t="n"/>
+      <c r="B17" s="69" t="n"/>
       <c r="C17" s="6" t="inlineStr">
         <is>
           <t>登录状态与异常访问控制</t>
@@ -1244,13 +1443,9 @@
       </c>
       <c r="H17" s="11" t="inlineStr"/>
     </row>
-    <row r="18" ht="44" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>管控</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="33" t="n"/>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>基础运维核查与权限管理</t>
         </is>
@@ -1282,17 +1477,9 @@
       </c>
       <c r="H18" s="11" t="inlineStr"/>
     </row>
-    <row r="19" ht="44" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>管控</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>基础运维核查与权限管理</t>
-        </is>
-      </c>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="33" t="n"/>
+      <c r="B19" s="69" t="n"/>
       <c r="C19" s="6" t="inlineStr">
         <is>
           <t>用户账号管理</t>
@@ -1320,61 +1507,57 @@
       </c>
       <c r="H19" s="11" t="inlineStr"/>
     </row>
-    <row r="20" ht="44" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>管控</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="69" t="n"/>
+      <c r="B20" s="45" t="inlineStr">
         <is>
           <t>基础运维核查与审计调取</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="37" t="inlineStr">
         <is>
           <t>归档/查询/导出操作日志记录</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="38" t="inlineStr">
         <is>
           <t>F06-01/02/03</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="46" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" s="40" t="inlineStr">
         <is>
           <t>模块 6</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="41" t="inlineStr">
         <is>
           <t>后端拦截埋点（谁/何时/操作了什么/结果）→ 审计表；查询界面按时间/用户/类型筛选</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr"/>
-    </row>
-    <row r="21" ht="44" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="H20" s="42" t="inlineStr"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="47" t="inlineStr">
         <is>
           <t>暂缓（Phase1.1/Phase2）</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="48" t="inlineStr">
         <is>
           <t>满足数据不出境合规要求</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="49" t="inlineStr">
         <is>
           <t>数据加密存储 + 密钥管理</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="50" t="inlineStr">
         <is>
           <t>F04-01/02</t>
         </is>
@@ -1384,39 +1567,35 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="51" t="inlineStr">
         <is>
           <t>模块 4</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="52" t="inlineStr">
         <is>
           <t>（后续）Key Vault CMK + 字段级 aes_encrypt + 掩码函数</t>
         </is>
       </c>
-      <c r="H21" s="17" t="inlineStr">
+      <c r="H21" s="53" t="inlineStr">
         <is>
           <t>依赖：PII 字段分级清单与合规口径定稿（法务）——先以 Azure 平台级 SSE 过渡，不阻塞上线</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="44" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>暂缓（Phase1.1/Phase2）</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="33" t="n"/>
+      <c r="B22" s="48" t="inlineStr">
         <is>
           <t>确保归档数据可恢复</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="49" t="inlineStr">
         <is>
           <t>数据备份管理 + 异地灾备</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="50" t="inlineStr">
         <is>
           <t>F04-03/04</t>
         </is>
@@ -1426,39 +1605,35 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F22" s="51" t="inlineStr">
         <is>
           <t>模块 4</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="G22" s="52" t="inlineStr">
         <is>
           <t>（后续）SQL PITR + 存储冗余 + 灾备演练</t>
         </is>
       </c>
-      <c r="H22" s="17" t="inlineStr">
+      <c r="H22" s="53" t="inlineStr">
         <is>
           <t>依赖：基础设施与灾备方案评审（平台团队）——Phase1 用云平台默认冗余过渡</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="44" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>暂缓（Phase1.1/Phase2）</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="33" t="n"/>
+      <c r="B23" s="48" t="inlineStr">
         <is>
           <t>归档记录定期删除与合规保留</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="49" t="inlineStr">
         <is>
           <t>Legal Hold 冻结</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="50" t="inlineStr">
         <is>
           <t>F03-02</t>
         </is>
@@ -1468,39 +1643,35 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F23" s="51" t="inlineStr">
         <is>
           <t>模块 3</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="G23" s="52" t="inlineStr">
         <is>
           <t>（后续）Hold/Release + 豁免 + 留痕（在处置引擎上扩展）</t>
         </is>
       </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="H23" s="53" t="inlineStr">
         <is>
           <t>依赖：Legal Hold 触发条件与审批流程定义（法务）——处置引擎（F03-01）本期交付，Hold 作为其扩展下期补</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="24" t="inlineStr">
-        <is>
-          <t>暂缓（Phase1.1/Phase2）</t>
-        </is>
-      </c>
-      <c r="B24" s="25" t="inlineStr">
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="33" t="n"/>
+      <c r="B24" s="48" t="inlineStr">
         <is>
           <t>确保迁移过程数据完整可追溯</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C24" s="54" t="inlineStr">
         <is>
           <t>迁移前基准记录 + 迁移后完整性比对</t>
         </is>
       </c>
-      <c r="D24" s="27" t="inlineStr">
+      <c r="D24" s="55" t="inlineStr">
         <is>
           <t>F01-04/05</t>
         </is>
@@ -1510,102 +1681,135 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="F24" s="29" t="inlineStr">
+      <c r="F24" s="56" t="inlineStr">
         <is>
           <t>模块 1</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="G24" s="52" t="inlineStr">
         <is>
           <t>（后续）基准快照 + 双向比对 + 差异报告</t>
         </is>
       </c>
-      <c r="H24" s="17" t="inlineStr">
+      <c r="H24" s="53" t="inlineStr">
         <is>
           <t>依赖：数据质量基线与对账方案确定——Phase1 先以导入成功行数核对过渡，不阻塞上线</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="24" t="inlineStr">
-        <is>
-          <t>暂缓（Phase1.1/Phase2）</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="inlineStr">
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="69" t="n"/>
+      <c r="B25" s="57" t="inlineStr">
         <is>
           <t>归档记录定期删除与合规保留</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
+      <c r="C25" s="58" t="inlineStr">
         <is>
           <t>保留期限到期自动删除</t>
         </is>
       </c>
-      <c r="D25" s="27" t="inlineStr">
+      <c r="D25" s="59" t="inlineStr">
         <is>
           <t>F03-01</t>
         </is>
       </c>
-      <c r="E25" s="28" t="inlineStr">
+      <c r="E25" s="60" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F25" s="29" t="inlineStr">
+      <c r="F25" s="61" t="inlineStr">
         <is>
           <t>模块 3</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="G25" s="62" t="inlineStr">
         <is>
           <t>（后续）保留策略→到期扫描→DROP PARTITION→VACUUM→留痕</t>
         </is>
       </c>
-      <c r="H25" s="17" t="inlineStr">
+      <c r="H25" s="63" t="inlineStr">
         <is>
           <t>依赖：保留期规则与处置审批流程定稿——Phase1 以文件手动删除（回收站）过渡</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="44" customHeight="1"/>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+    <row r="26" ht="42" customHeight="1"/>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="70" t="inlineStr">
         <is>
           <t>纳入统计：16 项技术功能（P0×10：F01-01/03、F05-01/02/03/04、F08-01/03、F06 三合一；P1×6：F01-02、F02-01/02、F05-05、F08-02/04/05）</t>
         </is>
       </c>
-    </row>
-    <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="B27" s="71" t="n"/>
+      <c r="C27" s="71" t="n"/>
+      <c r="D27" s="71" t="n"/>
+      <c r="E27" s="71" t="n"/>
+      <c r="F27" s="71" t="n"/>
+      <c r="G27" s="71" t="n"/>
+      <c r="H27" s="71" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="72" t="inlineStr">
         <is>
           <t>暂缓统计：5 组 10 项（加密×2 / 备份灾备×2 / Legal Hold×1 / 迁移完整性校验×2 / 到期自动删除×1）——均有过渡方案，不阻塞 Phase1 上线</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="B28" s="73" t="n"/>
+      <c r="C28" s="73" t="n"/>
+      <c r="D28" s="73" t="n"/>
+      <c r="E28" s="73" t="n"/>
+      <c r="F28" s="73" t="n"/>
+      <c r="G28" s="73" t="n"/>
+      <c r="H28" s="73" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="74" t="inlineStr">
         <is>
           <t>三层级读法：业务场景（为什么做）→ 业务功能（做什么）→ 技术功能（怎么做，含数据层处理：四层转换/分区/SAS）</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="B29" s="73" t="n"/>
+      <c r="C29" s="73" t="n"/>
+      <c r="D29" s="73" t="n"/>
+      <c r="E29" s="73" t="n"/>
+      <c r="F29" s="73" t="n"/>
+      <c r="G29" s="73" t="n"/>
+      <c r="H29" s="73" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="74" t="inlineStr">
         <is>
           <t>与计划对应：本表 P0+P1 = 项目执行计划2 周计划的开发范围；暂缓项在 Phase1.1（W13+）或 Phase2 排期</t>
         </is>
       </c>
-    </row>
-    <row r="31" ht="26" customHeight="1"/>
+      <c r="B30" s="73" t="n"/>
+      <c r="C30" s="73" t="n"/>
+      <c r="D30" s="73" t="n"/>
+      <c r="E30" s="73" t="n"/>
+      <c r="F30" s="73" t="n"/>
+      <c r="G30" s="73" t="n"/>
+      <c r="H30" s="73" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1"/>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="15">
+    <mergeCell ref="B10:B14"/>
     <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A21:A25"/>
     <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A5:A9"/>
+    <mergeCell ref="B18:B19"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A15:A20"/>
     <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A10:A14"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B15:B17"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A31:H31"/>
+    <mergeCell ref="B5:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1630,58 +1834,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>Phase 1 · Basic File Management（CHINA RIMS 英文版功能点 → 三层级总结）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="19" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>来源：CHINA RIMS SOLUTION PROPOSAL · Function Roadmap 1 —— 安全合规的手动文件上传与管理系统，确保 PI（个人信息）不出境 · OBJECTIVE：退役系统文件的手动上传/管理通道，PI 数据境内留存</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>业务场景</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>业务功能（英文原文）</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>业务功能（中文）</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr">
         <is>
           <t>技术功能（实现层）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t>数据/存储层处理</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="31" t="inlineStr">
         <is>
           <t>合规控制点</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>文件管理</t>
         </is>
@@ -1717,12 +1921,8 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>文件管理</t>
-        </is>
-      </c>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="33" t="n"/>
       <c r="B6" s="20" t="inlineStr">
         <is>
           <t>File deletion</t>
@@ -1750,41 +1950,37 @@
       </c>
       <c r="G6" s="22" t="inlineStr"/>
     </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>文件管理</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="69" t="n"/>
+      <c r="B7" s="45" t="inlineStr">
         <is>
           <t>File metadata mgmt.</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="64" t="inlineStr">
         <is>
           <t>文件元数据管理</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="65" t="inlineStr">
         <is>
           <t>元数据模型：来源系统/文件分类/业务时间/关联业务单号/标签；元数据编辑与查询界面</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="41" t="inlineStr">
         <is>
           <t>元数据库（Azure SQL）存储；文件 ↔ 元数据 ↔ 来源系统三方关联索引</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="66" t="inlineStr">
         <is>
           <t>元数据含 PI 标记字段（为后续脱敏/加密演进预留）</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr"/>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="G7" s="67" t="inlineStr"/>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="43" t="inlineStr">
         <is>
           <t>系统配置</t>
         </is>
@@ -1816,12 +2012,8 @@
       </c>
       <c r="G8" s="22" t="inlineStr"/>
     </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>系统配置</t>
-        </is>
-      </c>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="33" t="n"/>
       <c r="B9" s="20" t="inlineStr">
         <is>
           <t>Role permission mgmt.</t>
@@ -1849,41 +2041,37 @@
       </c>
       <c r="G9" s="22" t="inlineStr"/>
     </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>系统配置</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="69" t="n"/>
+      <c r="B10" s="45" t="inlineStr">
         <is>
           <t>Basic Data Mgmt.</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="64" t="inlineStr">
         <is>
           <t>基础数据管理</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="65" t="inlineStr">
         <is>
           <t>基础字典维护：来源系统清单、文件分类、保留期规则、标签字典等配置项管理界面</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="41" t="inlineStr">
         <is>
           <t>字典表 CRUD + 缓存；配置变更即生效（无需发版）</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="66" t="inlineStr">
         <is>
           <t>保留期规则为后续到期处置的输入</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr"/>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="G10" s="67" t="inlineStr"/>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="44" t="inlineStr">
         <is>
           <t>系统日志</t>
         </is>
@@ -1915,41 +2103,37 @@
       </c>
       <c r="G11" s="22" t="inlineStr"/>
     </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>系统日志</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="69" t="n"/>
+      <c r="B12" s="45" t="inlineStr">
         <is>
           <t>Audit Log</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="64" t="inlineStr">
         <is>
           <t>审计日志</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="65" t="inlineStr">
         <is>
           <t>面向合规审计的独立日志视图：按用户/时间/操作类型/文件检索；审计报表导出</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="41" t="inlineStr">
         <is>
           <t>审计日志独立存储（与操作日志分表）；导出受审计员权限控制</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="66" t="inlineStr">
         <is>
           <t>满足内外部审计调取（等保/内审）；导出本身也留痕</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr"/>
-    </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="G12" s="67" t="inlineStr"/>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="68" t="inlineStr">
         <is>
           <t>价值与目标</t>
         </is>
@@ -1981,12 +2165,8 @@
       </c>
       <c r="G13" s="22" t="inlineStr"/>
     </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
-        <is>
-          <t>价值与目标</t>
-        </is>
-      </c>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="33" t="n"/>
       <c r="B14" s="20" t="inlineStr">
         <is>
           <t>Immediately usable channel for decommissioning projects</t>
@@ -2018,71 +2198,90 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t>价值与目标</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="69" t="n"/>
+      <c r="B15" s="45" t="inlineStr">
         <is>
           <t>Foundation for later automation</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="64" t="inlineStr">
         <is>
           <t>后续自动化的地基</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="65" t="inlineStr">
         <is>
           <t>Phase1 建立的元数据模型/权限体系/审计框架/存储结构，直接支撑后续 Roadmap 的自动迁移与湖仓检索</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="41" t="inlineStr">
         <is>
           <t>存储与元数据结构按湖仓架构预留（Blob→ADLS/Iceberg 演进路径）</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="66" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="67" t="inlineStr">
         <is>
           <t>对应 VALUE 第 3 条</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
+    <row r="16" ht="42" customHeight="1"/>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="75" t="inlineStr">
         <is>
           <t>读法：业务场景（3+1 类）→ 业务功能（英文原文对照）→ 技术功能（怎么实现，含数据/存储层与合规控制点）</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="B17" s="76" t="n"/>
+      <c r="C17" s="76" t="n"/>
+      <c r="D17" s="76" t="n"/>
+      <c r="E17" s="76" t="n"/>
+      <c r="F17" s="76" t="n"/>
+      <c r="G17" s="76" t="n"/>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="74" t="inlineStr">
         <is>
           <t>与中文版功能列表的映射：File import ≈ F01-02 非结构化导入（手动版）；Metadata ≈ F02；User/Role ≈ F08；Operation/Audit Log ≈ F06；Deletion 为 Phase1 新增点（对应 F03 的简化版，本期做手动/逻辑删除，自动到期处置留待后续）</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="B18" s="73" t="n"/>
+      <c r="C18" s="73" t="n"/>
+      <c r="D18" s="73" t="n"/>
+      <c r="E18" s="73" t="n"/>
+      <c r="F18" s="73" t="n"/>
+      <c r="G18" s="73" t="n"/>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="74" t="inlineStr">
         <is>
           <t>英文版与中文版范围差异：英文 Roadmap 1 更聚焦"手动文件管理"（无批量抽取/在线检索/到期自动删除）——本表技术功能按 Azure B2 架构落地，后续 Roadmap 可平滑演进到自动迁移与湖仓检索</t>
         </is>
       </c>
+      <c r="B19" s="73" t="n"/>
+      <c r="C19" s="73" t="n"/>
+      <c r="D19" s="73" t="n"/>
+      <c r="E19" s="73" t="n"/>
+      <c r="F19" s="73" t="n"/>
+      <c r="G19" s="73" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A5:A7"/>
     <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/report/Phase1核心功能列表.xlsx
+++ b/report/Phase1核心功能列表.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="31">
+  <fonts count="39">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -196,8 +196,50 @@
       <color rgb="0092400E"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="8.800000000000001"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00475569"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -269,8 +311,23 @@
         <fgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F3FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -373,11 +430,77 @@
       </top>
       <bottom/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="0094A3B8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="0094A3B8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -591,6 +714,76 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -956,531 +1149,691 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="52" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="30" t="inlineStr">
-        <is>
-          <t>Phase 1 开发 · 核心功能列表（业务场景 → 业务功能 → 技术功能）</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Phase 1 开发 · 核心功能列表（业务场景 → 业务功能 → 技术功能 + 人天评估）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>纳入 19 项（P0 上线必备 11 / P1 重要 8），暂缓 7 项（加密/备份/灾备/Legal Hold——依赖外部决策，不阻塞上线，Phase1.1 或 Phase2 补齐）· 优先级：P0 = 上线门槛（缺一不能上线）；P1 = 重要（首个迭代内交付）；P2 = 暂缓</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="31" t="inlineStr">
+          <t>纳入 15 项（P0×10 / P1×5）· 人天按 前端(React) / 后端 API(.NET) / 数据(Databricks·Iceberg·SeaTunnel) 三线拆分评估 · 合计 76 人天（前端 25 + 后端 34 + 数据 17）· 已移除：登录状态与异常访问控制、迁移完整性校验、到期自动删除、加密、备份灾备、Legal Hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>业务场景</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>业务功能</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>技术功能（实现层）</t>
         </is>
       </c>
-      <c r="D4" s="31" t="inlineStr">
-        <is>
-          <t>对应功能列表编号</t>
-        </is>
-      </c>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>功能编号</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="F4" s="31" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>所属模块</t>
         </is>
       </c>
-      <c r="G4" s="31" t="inlineStr">
-        <is>
-          <t>技术要点/数据层处理</t>
-        </is>
-      </c>
-      <c r="H4" s="31" t="inlineStr">
-        <is>
-          <t>暂缓原因（如暂缓）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>人天评估（按技术线拆分）</t>
+        </is>
+      </c>
+      <c r="H4" s="77" t="n"/>
+      <c r="I4" s="78" t="n"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>人天小计</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>技术要点 / 备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="69" t="n"/>
+      <c r="B5" s="69" t="n"/>
+      <c r="C5" s="69" t="n"/>
+      <c r="D5" s="69" t="n"/>
+      <c r="E5" s="69" t="n"/>
+      <c r="F5" s="69" t="n"/>
+      <c r="G5" s="79" t="inlineStr">
+        <is>
+          <t>前端(React)</t>
+        </is>
+      </c>
+      <c r="H5" s="79" t="inlineStr">
+        <is>
+          <t>后端API(.NET)</t>
+        </is>
+      </c>
+      <c r="I5" s="79" t="inlineStr">
+        <is>
+          <t>数据(Databricks)</t>
+        </is>
+      </c>
+      <c r="J5" s="69" t="n"/>
+      <c r="K5" s="69" t="n"/>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="80" t="inlineStr">
         <is>
           <t>归档</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B6" s="81" t="inlineStr">
         <is>
           <t>退役系统历史数据全量入库归档</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C6" s="81" t="inlineStr">
         <is>
           <t>结构化历史数据批量导入</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D6" s="38" t="inlineStr">
         <is>
           <t>F01-01</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E6" s="82" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F6" s="40" t="inlineStr">
         <is>
           <t>模块 1</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>SeaTunnel JDBC 分片并行抽取（限速/断点续传）→ Iceberg RAW 层写入（Parquet+ZSTD，分区 sys_id+日期）；源库类型映射表</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr"/>
-    </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="33" t="n"/>
-      <c r="B6" s="33" t="n"/>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="G6" s="83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="84" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="85" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="86" t="n">
+        <v>8</v>
+      </c>
+      <c r="K6" s="87" t="inlineStr">
+        <is>
+          <t>SeaTunnel JDBC 分片抽取→Iceberg RAW 写入；断点续传；【数据】类型映射+分区设计</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="33" t="n"/>
+      <c r="B7" s="88" t="inlineStr">
+        <is>
+          <t>退役系统历史数据全量入库归档</t>
+        </is>
+      </c>
+      <c r="C7" s="88" t="inlineStr">
         <is>
           <t>非结构化文件及离线包批量导入</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>F01-02</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E7" s="89" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>模块 1</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>文件/离线介质 → Blob 附件账户（属性保留 + SHA-256 登记）；分片上传/断点续传</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr"/>
-    </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="33" t="n"/>
-      <c r="B7" s="69" t="n"/>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="G7" s="90" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H7" s="91" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="92" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="93" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K7" s="94" t="inlineStr">
+        <is>
+          <t>分片上传/压缩包解析；【数据】Blob 落地+SHA-256 登记</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="33" t="n"/>
+      <c r="B8" s="69" t="n"/>
+      <c r="C8" s="88" t="inlineStr">
         <is>
           <t>数据导入规则配置</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>F01-03</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E8" s="95" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>模块 1</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>源字段→RIMS 标准字段映射配置（元数据库存储）；配置生成器：勾选表 → 自动生成抽取任务</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr"/>
-    </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="33" t="n"/>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="G8" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="91" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="92" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="93" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" s="94" t="inlineStr">
+        <is>
+          <t>源字段→标准字段映射配置界面；配置生成器（勾选表→生成任务）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="33" t="n"/>
+      <c r="B9" s="88" t="inlineStr">
         <is>
           <t>多源异构数据接入与标准化</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C9" s="88" t="inlineStr">
         <is>
           <t>统一元数据模型</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>F02-01</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E9" s="89" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>模块 2</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>统一元数据字段体系（字段定义/类型/来源系统编码）；元数据库 35 表落地</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr"/>
-    </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="69" t="n"/>
-      <c r="B9" s="69" t="n"/>
-      <c r="C9" s="37" t="inlineStr">
+      <c r="G9" s="90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="91" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I9" s="92" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J9" s="93" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" s="94" t="inlineStr">
+        <is>
+          <t>元数据字段体系+35表落地；【数据】湖仓表结构注册</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="102" t="n"/>
+      <c r="B10" s="69" t="n"/>
+      <c r="C10" s="81" t="inlineStr">
         <is>
           <t>来源系统信息绑定</t>
         </is>
       </c>
-      <c r="D9" s="38" t="inlineStr">
+      <c r="D10" s="38" t="inlineStr">
         <is>
           <t>F02-02</t>
         </is>
       </c>
-      <c r="E9" s="39" t="inlineStr">
+      <c r="E10" s="96" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F9" s="40" t="inlineStr">
+      <c r="F10" s="40" t="inlineStr">
         <is>
           <t>模块 2</t>
         </is>
       </c>
-      <c r="G9" s="41" t="inlineStr">
-        <is>
-          <t>记录接入时绑定源系统编码与退役系统档案；数据血缘（哪条记录来自哪个源）</t>
-        </is>
-      </c>
-      <c r="H9" s="42" t="inlineStr"/>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="G10" s="83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="84" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I10" s="85" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J10" s="86" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" s="87" t="inlineStr">
+        <is>
+          <t>源系统编码绑定+数据血缘</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="97" t="inlineStr">
         <is>
           <t>检索</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B11" s="81" t="inlineStr">
         <is>
           <t>QA/IT 人员日常基础数据查阅</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C11" s="81" t="inlineStr">
         <is>
           <t>关键词检索</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>F05-01</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E11" s="82" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F11" s="40" t="inlineStr">
         <is>
           <t>模块 5</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>元数据驱动动态查询表单 → 查询代理（SQL 白名单+参数化拼装）→ Databricks SQL Warehouse（SERVE 层热表，分区裁剪）</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="inlineStr"/>
-    </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="33" t="n"/>
-      <c r="B11" s="33" t="n"/>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="G11" s="83" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="84" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="85" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="86" t="n">
+        <v>8</v>
+      </c>
+      <c r="K11" s="87" t="inlineStr">
+        <is>
+          <t>动态表单→查询代理（白名单+参数化）→Databricks SQL Warehouse；【数据】SERVE 热表</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="33" t="n"/>
+      <c r="B12" s="88" t="inlineStr">
+        <is>
+          <t>QA/IT 人员日常基础数据查阅</t>
+        </is>
+      </c>
+      <c r="C12" s="88" t="inlineStr">
         <is>
           <t>按系统名称检索</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>F05-02</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E12" s="95" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>模块 5</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>系统下拉（来源系统绑定 F02-02）+ catalog-per-system 路由到对应归档库</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr"/>
-    </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="33" t="n"/>
-      <c r="B12" s="33" t="n"/>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>按业务时间检索</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>F05-03</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>模块 5</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>时间区间 → Iceberg 分区裁剪（业务时间分区列）；避免全表扫描</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr"/>
-    </row>
-    <row r="13" ht="42" customHeight="1">
+      <c r="G12" s="90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="91" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I12" s="92" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J12" s="93" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" s="94" t="inlineStr">
+        <is>
+          <t>系统下拉+catalog 路由</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
       <c r="A13" s="33" t="n"/>
       <c r="B13" s="33" t="n"/>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="88" t="inlineStr">
+        <is>
+          <t>按业务时间检索</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>F05-03</t>
+        </is>
+      </c>
+      <c r="E13" s="95" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>模块 5</t>
+        </is>
+      </c>
+      <c r="G13" s="90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="91" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I13" s="92" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="93" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K13" s="94" t="inlineStr">
+        <is>
+          <t>时间区间→【数据】Iceberg 分区裁剪</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="33" t="n"/>
+      <c r="B14" s="33" t="n"/>
+      <c r="C14" s="88" t="inlineStr">
         <is>
           <t>检索结果列表展示</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>F05-04</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E14" s="95" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>模块 5</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>React 动态表格（元数据驱动列渲染/分页/排序/大批量懒加载）</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="inlineStr"/>
-    </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="69" t="n"/>
-      <c r="B14" s="69" t="n"/>
-      <c r="C14" s="37" t="inlineStr">
+      <c r="G14" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" s="91" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I14" s="92" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J14" s="93" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" s="94" t="inlineStr">
+        <is>
+          <t>元数据驱动动态表格（分页/排序/懒加载）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="102" t="n"/>
+      <c r="B15" s="69" t="n"/>
+      <c r="C15" s="81" t="inlineStr">
         <is>
           <t>原始文件在线预览</t>
         </is>
       </c>
-      <c r="D14" s="38" t="inlineStr">
+      <c r="D15" s="38" t="inlineStr">
         <is>
           <t>F05-05</t>
         </is>
       </c>
-      <c r="E14" s="39" t="inlineStr">
+      <c r="E15" s="96" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F14" s="40" t="inlineStr">
+      <c r="F15" s="40" t="inlineStr">
         <is>
           <t>模块 5</t>
         </is>
       </c>
-      <c r="G14" s="41" t="inlineStr">
-        <is>
-          <t>后端签发 SAS → 前端直连 Blob 预览（图片/常见文档），不经服务端中转</t>
-        </is>
-      </c>
-      <c r="H14" s="42" t="inlineStr"/>
-    </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="44" t="inlineStr">
+      <c r="G15" s="83" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H15" s="84" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="85" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="86" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K15" s="87" t="inlineStr">
+        <is>
+          <t>SAS 签发→前端直连 Blob 预览</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="98" t="inlineStr">
         <is>
           <t>管控</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B16" s="81" t="inlineStr">
         <is>
           <t>企业用户统一身份认证与访问</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C16" s="81" t="inlineStr">
         <is>
           <t>企业 SSO 集成</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D16" s="38" t="inlineStr">
         <is>
           <t>F08-03</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E16" s="82" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F16" s="40" t="inlineStr">
         <is>
           <t>模块 8</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>Entra ID OIDC 对接；JWT 角色 Claims；登录态管理</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr"/>
-    </row>
-    <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="33" t="n"/>
-      <c r="B16" s="33" t="n"/>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="G16" s="83" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H16" s="84" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I16" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="86" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" s="87" t="inlineStr">
+        <is>
+          <t>Entra ID OIDC+JWT Claims 贯通</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="33" t="n"/>
+      <c r="B17" s="88" t="inlineStr">
+        <is>
+          <t>企业用户统一身份认证与访问</t>
+        </is>
+      </c>
+      <c r="C17" s="88" t="inlineStr">
         <is>
           <t>用户身份自动识别与关联</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>F08-04</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E17" s="89" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>模块 8</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>企业身份 → RIMS 用户自动关联（首次登录建档）</t>
-        </is>
-      </c>
-      <c r="H16" s="11" t="inlineStr"/>
-    </row>
-    <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="33" t="n"/>
-      <c r="B17" s="69" t="n"/>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>登录状态与异常访问控制</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>F08-05</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="G17" s="90" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H17" s="91" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="93" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K17" s="94" t="inlineStr">
+        <is>
+          <t>首次登录自动建档关联</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="33" t="n"/>
+      <c r="B18" s="88" t="inlineStr">
+        <is>
+          <t>基础运维核查与权限管理</t>
+        </is>
+      </c>
+      <c r="C18" s="88" t="inlineStr">
+        <is>
+          <t>基础角色权限配置</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>F08-01</t>
+        </is>
+      </c>
+      <c r="E18" s="95" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>模块 8</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>会话超时/认证失败锁定/异常登录记录</t>
-        </is>
-      </c>
-      <c r="H17" s="11" t="inlineStr"/>
-    </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="33" t="n"/>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>基础运维核查与权限管理</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>基础角色权限配置</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>F08-01</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>模块 8</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>RBAC 基础三角色（管理员/查询员/审计员）；页面+数据双层权限</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="inlineStr"/>
-    </row>
-    <row r="19" ht="42" customHeight="1">
+      <c r="G18" s="90" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H18" s="91" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I18" s="92" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="93" t="n">
+        <v>7</v>
+      </c>
+      <c r="K18" s="94" t="inlineStr">
+        <is>
+          <t>RBAC 三角色；菜单/按钮/数据三层；【数据】UC GRANT 对接</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
       <c r="A19" s="33" t="n"/>
       <c r="B19" s="69" t="n"/>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="88" t="inlineStr">
         <is>
           <t>用户账号管理</t>
         </is>
@@ -1490,7 +1843,7 @@
           <t>F08-02</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="89" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -1500,316 +1853,146 @@
           <t>模块 8</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>账号启用/禁用/重置（SSO 体系下的本地映射管理）</t>
-        </is>
-      </c>
-      <c r="H19" s="11" t="inlineStr"/>
-    </row>
-    <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="69" t="n"/>
-      <c r="B20" s="45" t="inlineStr">
+      <c r="G19" s="90" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H19" s="91" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="93" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K19" s="94" t="inlineStr">
+        <is>
+          <t>账号启用/禁用/重置（SSO 映射管理）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="102" t="n"/>
+      <c r="B20" s="88" t="inlineStr">
         <is>
           <t>基础运维核查与审计调取</t>
         </is>
       </c>
-      <c r="C20" s="37" t="inlineStr">
+      <c r="C20" s="88" t="inlineStr">
         <is>
           <t>归档/查询/导出操作日志记录</t>
         </is>
       </c>
-      <c r="D20" s="38" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>F06-01/02/03</t>
         </is>
       </c>
-      <c r="E20" s="46" t="inlineStr">
+      <c r="E20" s="95" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F20" s="40" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>模块 6</t>
         </is>
       </c>
-      <c r="G20" s="41" t="inlineStr">
-        <is>
-          <t>后端拦截埋点（谁/何时/操作了什么/结果）→ 审计表；查询界面按时间/用户/类型筛选</t>
-        </is>
-      </c>
-      <c r="H20" s="42" t="inlineStr"/>
-    </row>
-    <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="47" t="inlineStr">
-        <is>
-          <t>暂缓（Phase1.1/Phase2）</t>
-        </is>
-      </c>
-      <c r="B21" s="48" t="inlineStr">
-        <is>
-          <t>满足数据不出境合规要求</t>
-        </is>
-      </c>
-      <c r="C21" s="49" t="inlineStr">
-        <is>
-          <t>数据加密存储 + 密钥管理</t>
-        </is>
-      </c>
-      <c r="D21" s="50" t="inlineStr">
-        <is>
-          <t>F04-01/02</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F21" s="51" t="inlineStr">
-        <is>
-          <t>模块 4</t>
-        </is>
-      </c>
-      <c r="G21" s="52" t="inlineStr">
-        <is>
-          <t>（后续）Key Vault CMK + 字段级 aes_encrypt + 掩码函数</t>
-        </is>
-      </c>
-      <c r="H21" s="53" t="inlineStr">
-        <is>
-          <t>依赖：PII 字段分级清单与合规口径定稿（法务）——先以 Azure 平台级 SSE 过渡，不阻塞上线</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="33" t="n"/>
-      <c r="B22" s="48" t="inlineStr">
-        <is>
-          <t>确保归档数据可恢复</t>
-        </is>
-      </c>
-      <c r="C22" s="49" t="inlineStr">
-        <is>
-          <t>数据备份管理 + 异地灾备</t>
-        </is>
-      </c>
-      <c r="D22" s="50" t="inlineStr">
-        <is>
-          <t>F04-03/04</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F22" s="51" t="inlineStr">
-        <is>
-          <t>模块 4</t>
-        </is>
-      </c>
-      <c r="G22" s="52" t="inlineStr">
-        <is>
-          <t>（后续）SQL PITR + 存储冗余 + 灾备演练</t>
-        </is>
-      </c>
-      <c r="H22" s="53" t="inlineStr">
-        <is>
-          <t>依赖：基础设施与灾备方案评审（平台团队）——Phase1 用云平台默认冗余过渡</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="33" t="n"/>
-      <c r="B23" s="48" t="inlineStr">
-        <is>
-          <t>归档记录定期删除与合规保留</t>
-        </is>
-      </c>
-      <c r="C23" s="49" t="inlineStr">
-        <is>
-          <t>Legal Hold 冻结</t>
-        </is>
-      </c>
-      <c r="D23" s="50" t="inlineStr">
-        <is>
-          <t>F03-02</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F23" s="51" t="inlineStr">
-        <is>
-          <t>模块 3</t>
-        </is>
-      </c>
-      <c r="G23" s="52" t="inlineStr">
-        <is>
-          <t>（后续）Hold/Release + 豁免 + 留痕（在处置引擎上扩展）</t>
-        </is>
-      </c>
-      <c r="H23" s="53" t="inlineStr">
-        <is>
-          <t>依赖：Legal Hold 触发条件与审批流程定义（法务）——处置引擎（F03-01）本期交付，Hold 作为其扩展下期补</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="33" t="n"/>
-      <c r="B24" s="48" t="inlineStr">
-        <is>
-          <t>确保迁移过程数据完整可追溯</t>
-        </is>
-      </c>
-      <c r="C24" s="54" t="inlineStr">
-        <is>
-          <t>迁移前基准记录 + 迁移后完整性比对</t>
-        </is>
-      </c>
-      <c r="D24" s="55" t="inlineStr">
-        <is>
-          <t>F01-04/05</t>
-        </is>
-      </c>
-      <c r="E24" s="28" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F24" s="56" t="inlineStr">
-        <is>
-          <t>模块 1</t>
-        </is>
-      </c>
-      <c r="G24" s="52" t="inlineStr">
-        <is>
-          <t>（后续）基准快照 + 双向比对 + 差异报告</t>
-        </is>
-      </c>
-      <c r="H24" s="53" t="inlineStr">
-        <is>
-          <t>依赖：数据质量基线与对账方案确定——Phase1 先以导入成功行数核对过渡，不阻塞上线</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="69" t="n"/>
-      <c r="B25" s="57" t="inlineStr">
-        <is>
-          <t>归档记录定期删除与合规保留</t>
-        </is>
-      </c>
-      <c r="C25" s="58" t="inlineStr">
-        <is>
-          <t>保留期限到期自动删除</t>
-        </is>
-      </c>
-      <c r="D25" s="59" t="inlineStr">
-        <is>
-          <t>F03-01</t>
-        </is>
-      </c>
-      <c r="E25" s="60" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F25" s="61" t="inlineStr">
-        <is>
-          <t>模块 3</t>
-        </is>
-      </c>
-      <c r="G25" s="62" t="inlineStr">
-        <is>
-          <t>（后续）保留策略→到期扫描→DROP PARTITION→VACUUM→留痕</t>
-        </is>
-      </c>
-      <c r="H25" s="63" t="inlineStr">
-        <is>
-          <t>依赖：保留期规则与处置审批流程定稿——Phase1 以文件手动删除（回收站）过渡</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="42" customHeight="1"/>
-    <row r="27" ht="42" customHeight="1">
-      <c r="A27" s="70" t="inlineStr">
-        <is>
-          <t>纳入统计：16 项技术功能（P0×10：F01-01/03、F05-01/02/03/04、F08-01/03、F06 三合一；P1×6：F01-02、F02-01/02、F05-05、F08-02/04/05）</t>
-        </is>
-      </c>
-      <c r="B27" s="71" t="n"/>
-      <c r="C27" s="71" t="n"/>
-      <c r="D27" s="71" t="n"/>
-      <c r="E27" s="71" t="n"/>
-      <c r="F27" s="71" t="n"/>
-      <c r="G27" s="71" t="n"/>
-      <c r="H27" s="71" t="n"/>
-    </row>
-    <row r="28" ht="42" customHeight="1">
-      <c r="A28" s="72" t="inlineStr">
-        <is>
-          <t>暂缓统计：5 组 10 项（加密×2 / 备份灾备×2 / Legal Hold×1 / 迁移完整性校验×2 / 到期自动删除×1）——均有过渡方案，不阻塞 Phase1 上线</t>
-        </is>
-      </c>
-      <c r="B28" s="73" t="n"/>
-      <c r="C28" s="73" t="n"/>
-      <c r="D28" s="73" t="n"/>
-      <c r="E28" s="73" t="n"/>
-      <c r="F28" s="73" t="n"/>
-      <c r="G28" s="73" t="n"/>
-      <c r="H28" s="73" t="n"/>
-    </row>
-    <row r="29" ht="42" customHeight="1">
-      <c r="A29" s="74" t="inlineStr">
-        <is>
-          <t>三层级读法：业务场景（为什么做）→ 业务功能（做什么）→ 技术功能（怎么做，含数据层处理：四层转换/分区/SAS）</t>
-        </is>
-      </c>
-      <c r="B29" s="73" t="n"/>
-      <c r="C29" s="73" t="n"/>
-      <c r="D29" s="73" t="n"/>
-      <c r="E29" s="73" t="n"/>
-      <c r="F29" s="73" t="n"/>
-      <c r="G29" s="73" t="n"/>
-      <c r="H29" s="73" t="n"/>
-    </row>
-    <row r="30" ht="42" customHeight="1">
-      <c r="A30" s="74" t="inlineStr">
-        <is>
-          <t>与计划对应：本表 P0+P1 = 项目执行计划2 周计划的开发范围；暂缓项在 Phase1.1（W13+）或 Phase2 排期</t>
-        </is>
-      </c>
-      <c r="B30" s="73" t="n"/>
-      <c r="C30" s="73" t="n"/>
-      <c r="D30" s="73" t="n"/>
-      <c r="E30" s="73" t="n"/>
-      <c r="F30" s="73" t="n"/>
-      <c r="G30" s="73" t="n"/>
-      <c r="H30" s="73" t="n"/>
-    </row>
-    <row r="31" ht="42" customHeight="1"/>
+      <c r="G20" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="91" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I20" s="92" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="93" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K20" s="94" t="inlineStr">
+        <is>
+          <t>拦截埋点→审计表；审计查询界面；【数据】Databricks 查询日志对接</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="99" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B21" s="100" t="n"/>
+      <c r="C21" s="100" t="inlineStr">
+        <is>
+          <t>15 项技术功能</t>
+        </is>
+      </c>
+      <c r="D21" s="100" t="n"/>
+      <c r="E21" s="100" t="n"/>
+      <c r="F21" s="100" t="n"/>
+      <c r="G21" s="99" t="n">
+        <v>25</v>
+      </c>
+      <c r="H21" s="99" t="n">
+        <v>34</v>
+      </c>
+      <c r="I21" s="99" t="n">
+        <v>17</v>
+      </c>
+      <c r="J21" s="99" t="n">
+        <v>76</v>
+      </c>
+      <c r="K21" s="100" t="inlineStr">
+        <is>
+          <t>前端 25.0 + 后端 34.0 + 数据 17.0 人天（未含联调/测试/上线，建议整体 ×1.4 风险系数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>人天口径：前端 = React 界面开发；后端 API = .NET 服务开发；数据 = Databricks/Iceberg/SeaTunnel 对接与数据处理（含 UC 权限、SQL Warehouse 查询、四层落地）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>合计 76.0 人天为纯开发人天；含联调/测试/修复/上线建议 ×1.4 ≈ 106 人天 —— 对应 3 人团队约 9~10 周开发期（与项目执行计划2 的 W3~W10 吻合）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>已移除项（不在本期范围）：F08-05 登录状态与异常访问控制（SSO 平台侧已覆盖基础控制）、F01-04/05 迁移完整性校验、F03-01 到期自动删除、F04 加密/密钥、F04-03/04 备份灾备、F03-02 Legal Hold</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B10:B14"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A21:A25"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A5:A9"/>
+  <mergeCells count="21">
     <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A15:A20"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A10:A14"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="A11:A15"/>
+    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="A16:A20"/>
+    <mergeCell ref="B7:B8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2238,12 +2421,12 @@
           <t>读法：业务场景（3+1 类）→ 业务功能（英文原文对照）→ 技术功能（怎么实现，含数据/存储层与合规控制点）</t>
         </is>
       </c>
-      <c r="B17" s="76" t="n"/>
-      <c r="C17" s="76" t="n"/>
-      <c r="D17" s="76" t="n"/>
-      <c r="E17" s="76" t="n"/>
-      <c r="F17" s="76" t="n"/>
-      <c r="G17" s="76" t="n"/>
+      <c r="B17" s="101" t="n"/>
+      <c r="C17" s="101" t="n"/>
+      <c r="D17" s="101" t="n"/>
+      <c r="E17" s="101" t="n"/>
+      <c r="F17" s="101" t="n"/>
+      <c r="G17" s="101" t="n"/>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="74" t="inlineStr">
@@ -2251,12 +2434,6 @@
           <t>与中文版功能列表的映射：File import ≈ F01-02 非结构化导入（手动版）；Metadata ≈ F02；User/Role ≈ F08；Operation/Audit Log ≈ F06；Deletion 为 Phase1 新增点（对应 F03 的简化版，本期做手动/逻辑删除，自动到期处置留待后续）</t>
         </is>
       </c>
-      <c r="B18" s="73" t="n"/>
-      <c r="C18" s="73" t="n"/>
-      <c r="D18" s="73" t="n"/>
-      <c r="E18" s="73" t="n"/>
-      <c r="F18" s="73" t="n"/>
-      <c r="G18" s="73" t="n"/>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="74" t="inlineStr">
@@ -2264,12 +2441,6 @@
           <t>英文版与中文版范围差异：英文 Roadmap 1 更聚焦"手动文件管理"（无批量抽取/在线检索/到期自动删除）——本表技术功能按 Azure B2 架构落地，后续 Roadmap 可平滑演进到自动迁移与湖仓检索</t>
         </is>
       </c>
-      <c r="B19" s="73" t="n"/>
-      <c r="C19" s="73" t="n"/>
-      <c r="D19" s="73" t="n"/>
-      <c r="E19" s="73" t="n"/>
-      <c r="F19" s="73" t="n"/>
-      <c r="G19" s="73" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/report/Phase1核心功能列表.xlsx
+++ b/report/Phase1核心功能列表.xlsx
@@ -500,7 +500,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -784,6 +784,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1175,7 +1178,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>纳入 15 项（P0×10 / P1×5）· 人天按 前端(React) / 后端 API(.NET) / 数据(Databricks·Iceberg·SeaTunnel) 三线拆分评估 · 合计 76 人天（前端 25 + 后端 34 + 数据 17）· 已移除：登录状态与异常访问控制、迁移完整性校验、到期自动删除、加密、备份灾备、Legal Hold</t>
+          <t>纳入 15 项（P0×10 / P1×5）· 人天按 前端(React) / 后端 API(.NET) / 数据(Databricks) 三线拆分 · 合计 89.5 人天（前端 25.0 + 后端 52.0 + 数据 12.5）· 口径：数据列仅计 Databricks 相关 effort；后端按团队无 .NET 经验加成</t>
         </is>
       </c>
     </row>
@@ -1288,17 +1291,17 @@
         <v>1</v>
       </c>
       <c r="H6" s="84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" s="85" t="n">
         <v>5</v>
       </c>
       <c r="J6" s="86" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K6" s="87" t="inlineStr">
         <is>
-          <t>SeaTunnel JDBC 分片抽取→Iceberg RAW 写入；断点续传；【数据】类型映射+分区设计</t>
+          <t>SeaTunnel JDBC 分片抽取→Iceberg RAW 写入；断点续传；【数据】类型映射+分区设计 ｜BE+.NET 学习曲线</t>
         </is>
       </c>
     </row>
@@ -1333,17 +1336,17 @@
         <v>1.5</v>
       </c>
       <c r="H7" s="91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" s="92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" s="93" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="K7" s="94" t="inlineStr">
         <is>
-          <t>分片上传/压缩包解析；【数据】Blob 落地+SHA-256 登记</t>
+          <t>分片上传/压缩包解析；【数据】Blob 落地+SHA-256 登记 ｜Blob 操作无 Databricks</t>
         </is>
       </c>
     </row>
@@ -1374,13 +1377,13 @@
         <v>2</v>
       </c>
       <c r="H8" s="91" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="I8" s="92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="93" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="K8" s="94" t="inlineStr">
         <is>
@@ -1419,17 +1422,17 @@
         <v>1</v>
       </c>
       <c r="H9" s="91" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="I9" s="92" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J9" s="93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K9" s="94" t="inlineStr">
         <is>
-          <t>元数据字段体系+35表落地；【数据】湖仓表结构注册</t>
+          <t>元数据字段体系+35表落地；【数据】湖仓表结构注册 ｜DA=湖仓表结构注册(Databricks)</t>
         </is>
       </c>
     </row>
@@ -1460,13 +1463,13 @@
         <v>1</v>
       </c>
       <c r="H10" s="84" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="I10" s="85" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J10" s="86" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K10" s="87" t="inlineStr">
         <is>
@@ -1509,17 +1512,17 @@
         <v>3</v>
       </c>
       <c r="H11" s="84" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I11" s="85" t="n">
         <v>3</v>
       </c>
-      <c r="I11" s="85" t="n">
-        <v>2</v>
-      </c>
       <c r="J11" s="86" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="K11" s="87" t="inlineStr">
         <is>
-          <t>动态表单→查询代理（白名单+参数化）→Databricks SQL Warehouse；【数据】SERVE 热表</t>
+          <t>动态表单→查询代理（白名单+参数化）→Databricks SQL Warehouse；【数据】SERVE 热表 ｜DA=SQL Warehouse 对接+SERVE</t>
         </is>
       </c>
     </row>
@@ -1554,13 +1557,13 @@
         <v>1</v>
       </c>
       <c r="H12" s="91" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="I12" s="92" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J12" s="93" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K12" s="94" t="inlineStr">
         <is>
@@ -1595,17 +1598,17 @@
         <v>1</v>
       </c>
       <c r="H13" s="91" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="I13" s="92" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="93" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="K13" s="94" t="inlineStr">
         <is>
-          <t>时间区间→【数据】Iceberg 分区裁剪</t>
+          <t>时间区间→【数据】Iceberg 分区裁剪 ｜DA=分区裁剪验证</t>
         </is>
       </c>
     </row>
@@ -1636,13 +1639,13 @@
         <v>3</v>
       </c>
       <c r="H14" s="91" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="I14" s="92" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J14" s="93" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K14" s="94" t="inlineStr">
         <is>
@@ -1677,17 +1680,17 @@
         <v>2.5</v>
       </c>
       <c r="H15" s="84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15" s="85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" s="86" t="n">
         <v>5.5</v>
       </c>
       <c r="K15" s="87" t="inlineStr">
         <is>
-          <t>SAS 签发→前端直连 Blob 预览</t>
+          <t>SAS 签发→前端直连 Blob 预览 ｜SAS/Blob 无 Databricks</t>
         </is>
       </c>
     </row>
@@ -1726,13 +1729,13 @@
         <v>1.5</v>
       </c>
       <c r="H16" s="84" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="I16" s="85" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="86" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="K16" s="87" t="inlineStr">
         <is>
@@ -1771,13 +1774,13 @@
         <v>0.5</v>
       </c>
       <c r="H17" s="91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17" s="92" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="93" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="K17" s="94" t="inlineStr">
         <is>
@@ -1816,17 +1819,17 @@
         <v>2.5</v>
       </c>
       <c r="H18" s="91" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="I18" s="92" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J18" s="93" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K18" s="94" t="inlineStr">
         <is>
-          <t>RBAC 三角色；菜单/按钮/数据三层；【数据】UC GRANT 对接</t>
+          <t>RBAC 三角色；菜单/按钮/数据三层；【数据】UC GRANT 对接 ｜DA=UC GRANT 对接</t>
         </is>
       </c>
     </row>
@@ -1857,13 +1860,13 @@
         <v>1.5</v>
       </c>
       <c r="H19" s="91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I19" s="92" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="93" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="K19" s="94" t="inlineStr">
         <is>
@@ -1902,17 +1905,17 @@
         <v>2</v>
       </c>
       <c r="H20" s="91" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="I20" s="92" t="n">
         <v>1</v>
       </c>
       <c r="J20" s="93" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="K20" s="94" t="inlineStr">
         <is>
-          <t>拦截埋点→审计表；审计查询界面；【数据】Databricks 查询日志对接</t>
+          <t>拦截埋点→审计表；审计查询界面；【数据】Databricks 查询日志对接 ｜DA=Databricks 查询日志对接</t>
         </is>
       </c>
     </row>
@@ -1935,31 +1938,34 @@
         <v>25</v>
       </c>
       <c r="H21" s="99" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="I21" s="99" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="J21" s="99" t="n">
-        <v>76</v>
+        <v>89.5</v>
       </c>
       <c r="K21" s="100" t="inlineStr">
         <is>
-          <t>前端 25.0 + 后端 34.0 + 数据 17.0 人天（未含联调/测试/上线，建议整体 ×1.4 风险系数）</t>
-        </is>
-      </c>
+          <t>前端 25.0 + 后端 52.0（含 .NET 学习曲线加成）+ 数据 12.5（仅 Databricks 相关项）人天</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="103" t="n"/>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>人天口径：前端 = React 界面开发；后端 API = .NET 服务开发；数据 = Databricks/Iceberg/SeaTunnel 对接与数据处理（含 UC 权限、SQL Warehouse 查询、四层落地）</t>
+          <t>人天口径：前端 = React 界面；后端 API = .NET 服务开发（团队无 .NET 经验，已按学习曲线加成约 ×1.5）；数据 = 仅 Databricks/Iceberg/SeaTunnel/UC 相关 effort（Blob/元数据库操作计入后端，不占数据列）</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>合计 76.0 人天为纯开发人天；含联调/测试/修复/上线建议 ×1.4 ≈ 106 人天 —— 对应 3 人团队约 9~10 周开发期（与项目执行计划2 的 W3~W10 吻合）</t>
+          <t>合计 89.5 人天为纯开发人天；含联调/测试/修复/上线建议 ×1.4 ≈ 125 人天 —— 对应 3 人团队开发期与项目执行计划2 对齐</t>
         </is>
       </c>
     </row>
@@ -2445,9 +2451,9 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A19:G19"/>
